--- a/data/Blumenau/Abril 2023 - Super Hanes.xlsx
+++ b/data/Blumenau/Abril 2023 - Super Hanes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bttom\OneDrive - FURB\Documentos\GitHub\CidadaniaFinanceira\data\Blumenau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA015BD-817C-4692-8FE5-5B02209D1EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7CC0A7-6FF6-4A7C-B986-76550EA9C567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2025" yWindow="-13620" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="61">
   <si>
     <t>MERCADO</t>
   </si>
@@ -138,15 +138,6 @@
   </si>
   <si>
     <t>Pote</t>
-  </si>
-  <si>
-    <t>Dualis</t>
-  </si>
-  <si>
-    <t>Delicata</t>
-  </si>
-  <si>
-    <t>Claybom</t>
   </si>
   <si>
     <t>Óleo de Soja</t>
@@ -1249,7 +1240,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F5" s="35"/>
       <c r="G5" s="35"/>
@@ -1536,18 +1527,12 @@
       <c r="E17" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="I17" s="52">
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="52" t="e">
         <f>AVERAGE(F18:H18)</f>
-        <v>6.3233333333333333</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -1558,26 +1543,20 @@
       <c r="E18" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="30">
-        <v>4.99</v>
-      </c>
-      <c r="G18" s="30">
-        <v>5.99</v>
-      </c>
-      <c r="H18" s="31">
-        <v>7.99</v>
-      </c>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="31"/>
       <c r="I18" s="53"/>
     </row>
     <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="38" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D19" s="42">
         <v>0.9</v>
@@ -1586,13 +1565,13 @@
         <v>12</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I19" s="44">
         <f>AVERAGE(F20:H20)</f>
@@ -1620,10 +1599,10 @@
     </row>
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="46" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C21" s="48" t="s">
         <v>11</v>
@@ -1635,13 +1614,13 @@
         <v>12</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H21" s="28" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I21" s="52">
         <f>AVERAGE(F22:H22)</f>
@@ -1669,10 +1648,10 @@
     </row>
     <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="38" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C23" s="40" t="s">
         <v>11</v>
@@ -1684,7 +1663,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="22"/>
@@ -1710,10 +1689,10 @@
     </row>
     <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="46" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C25" s="48" t="s">
         <v>11</v>
@@ -1725,7 +1704,7 @@
         <v>12</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G25" s="27"/>
       <c r="H25" s="28"/>
@@ -1751,10 +1730,10 @@
     </row>
     <row r="27" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="57" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B27" s="59" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C27" s="59" t="s">
         <v>11</v>
@@ -1766,7 +1745,7 @@
         <v>12</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="22"/>
@@ -1792,13 +1771,13 @@
     </row>
     <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="46" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D29" s="50">
         <v>1</v>
@@ -1807,13 +1786,13 @@
         <v>12</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G29" s="27" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H29" s="28" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I29" s="52">
         <f>AVERAGE(F30:H30)</f>
@@ -1841,10 +1820,10 @@
     </row>
     <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="57" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B31" s="59" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C31" s="59" t="s">
         <v>11</v>
@@ -1856,10 +1835,10 @@
         <v>12</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H31" s="22"/>
       <c r="I31" s="44">
